--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -187,6 +187,12 @@
     <t>millimeter of mercury</t>
   </si>
   <si>
+    <t>mmol/L</t>
+  </si>
+  <si>
+    <t>millimole per liter</t>
+  </si>
+  <si>
     <t>{Number}</t>
   </si>
   <si>
@@ -230,6 +236,12 @@
   </si>
   <si>
     <t>one per 30 seconds</t>
+  </si>
+  <si>
+    <t>1/60sec</t>
+  </si>
+  <si>
+    <t>one per 60 seconds</t>
   </si>
   <si>
     <t>percentpoint</t>
@@ -505,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -733,9 +745,7 @@
       <c r="A14" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>58</v>
-      </c>
+      <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>36</v>
       </c>
@@ -829,6 +839,23 @@
       </c>
       <c r="E19" t="s" s="2">
         <v>68</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -860,7 +887,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>32</v>
@@ -877,36 +904,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-ucum-to-printsymbol.xlsx
+++ b/fhir/conceptmap-ucum-to-printsymbol.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
